--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123229249</v>
+        <v>123218761</v>
       </c>
       <c r="B5" t="n">
-        <v>95136</v>
+        <v>91507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>3884</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567211</v>
+        <v>567239</v>
       </c>
       <c r="R5" t="n">
-        <v>6509720</v>
+        <v>6509717</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123238999</v>
+        <v>123229249</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,49 +1117,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Sjöberga, Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567283</v>
+        <v>567211</v>
       </c>
       <c r="R6" t="n">
-        <v>6509723</v>
+        <v>6509720</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,29 +1189,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123218761</v>
+        <v>123238999</v>
       </c>
       <c r="B7" t="n">
-        <v>91507</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,41 +1219,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3884</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sjöberga, Sjöberga, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567239</v>
+        <v>567283</v>
       </c>
       <c r="R7" t="n">
-        <v>6509717</v>
+        <v>6509723</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,18 +1299,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123238970</v>
+        <v>123229402</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -710,26 +710,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567256</v>
+        <v>567250</v>
       </c>
       <c r="R2" t="n">
-        <v>6509747</v>
+        <v>6509796</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,29 +768,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123238954</v>
+        <v>123238970</v>
       </c>
       <c r="B3" t="n">
-        <v>79384</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567475</v>
+        <v>567256</v>
       </c>
       <c r="R3" t="n">
-        <v>6509855</v>
+        <v>6509747</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123238989</v>
+        <v>123238999</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -927,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -940,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567255</v>
+        <v>567283</v>
       </c>
       <c r="R4" t="n">
-        <v>6509736</v>
+        <v>6509723</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1105,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123229249</v>
+        <v>123220975</v>
       </c>
       <c r="B6" t="n">
-        <v>95136</v>
+        <v>83365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,37 +1126,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>1444</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sjöberga, Sjöberga, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567211</v>
+        <v>567466</v>
       </c>
       <c r="R6" t="n">
-        <v>6509720</v>
+        <v>6510055</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123238999</v>
+        <v>123238960</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>79384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,35 +1224,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567283</v>
+        <v>567474</v>
       </c>
       <c r="R7" t="n">
-        <v>6509723</v>
+        <v>6509777</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123229402</v>
+        <v>123238989</v>
       </c>
       <c r="B8" t="n">
         <v>98365</v>
@@ -1353,27 +1353,26 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567250</v>
+        <v>567255</v>
       </c>
       <c r="R8" t="n">
-        <v>6509796</v>
+        <v>6509736</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1411,28 +1410,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123220975</v>
+        <v>123229249</v>
       </c>
       <c r="B9" t="n">
-        <v>83365</v>
+        <v>95136</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,37 +1445,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1444</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Sjöberga, Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567466</v>
+        <v>567211</v>
       </c>
       <c r="R9" t="n">
-        <v>6510055</v>
+        <v>6509720</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123238960</v>
+        <v>123238954</v>
       </c>
       <c r="B10" t="n">
         <v>79384</v>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567474</v>
+        <v>567475</v>
       </c>
       <c r="R10" t="n">
-        <v>6509777</v>
+        <v>6509855</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123229402</v>
+        <v>123238979</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>79384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567250</v>
+        <v>567291</v>
       </c>
       <c r="R2" t="n">
-        <v>6509796</v>
+        <v>6509745</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -768,28 +762,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123238970</v>
+        <v>123229249</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,49 +793,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Sjöberga, Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567256</v>
+        <v>567211</v>
       </c>
       <c r="R3" t="n">
-        <v>6509747</v>
+        <v>6509720</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,19 +865,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1008,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123218761</v>
+        <v>123238989</v>
       </c>
       <c r="B5" t="n">
-        <v>91507</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,41 +1006,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3884</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sjöberga, Sjöberga, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567239</v>
+        <v>567255</v>
       </c>
       <c r="R5" t="n">
-        <v>6509717</v>
+        <v>6509736</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,28 +1086,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123220975</v>
+        <v>123238954</v>
       </c>
       <c r="B6" t="n">
-        <v>83365</v>
+        <v>79384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,41 +1117,44 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1444</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567466</v>
+        <v>567475</v>
       </c>
       <c r="R6" t="n">
-        <v>6510055</v>
+        <v>6509855</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,28 +1192,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123238960</v>
+        <v>123229402</v>
       </c>
       <c r="B7" t="n">
-        <v>79384</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,44 +1223,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567474</v>
+        <v>567250</v>
       </c>
       <c r="R7" t="n">
-        <v>6509777</v>
+        <v>6509796</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,29 +1304,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123238989</v>
+        <v>123218761</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>91507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1330,49 +1334,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>3884</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Sjöberga, Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567255</v>
+        <v>567239</v>
       </c>
       <c r="R8" t="n">
-        <v>6509736</v>
+        <v>6509717</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1410,29 +1406,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123229249</v>
+        <v>123238970</v>
       </c>
       <c r="B9" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,41 +1436,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sjöberga, Sjöberga, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567211</v>
+        <v>567256</v>
       </c>
       <c r="R9" t="n">
-        <v>6509720</v>
+        <v>6509747</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,28 +1516,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123238954</v>
+        <v>123220975</v>
       </c>
       <c r="B10" t="n">
-        <v>79384</v>
+        <v>83365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1543,44 +1547,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1444</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567475</v>
+        <v>567466</v>
       </c>
       <c r="R10" t="n">
-        <v>6509855</v>
+        <v>6510055</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1618,26 +1619,25 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123238979</v>
+        <v>123238960</v>
       </c>
       <c r="B11" t="n">
         <v>79384</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567291</v>
+        <v>567474</v>
       </c>
       <c r="R11" t="n">
-        <v>6509745</v>
+        <v>6509777</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123238979</v>
+        <v>123238999</v>
       </c>
       <c r="B2" t="n">
-        <v>79384</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567291</v>
+        <v>567283</v>
       </c>
       <c r="R2" t="n">
-        <v>6509745</v>
+        <v>6509723</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -784,7 +789,7 @@
         <v>123229249</v>
       </c>
       <c r="B3" t="n">
-        <v>95136</v>
+        <v>95139</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -883,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123238999</v>
+        <v>123238989</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,7 +923,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -931,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567283</v>
+        <v>567255</v>
       </c>
       <c r="R4" t="n">
-        <v>6509723</v>
+        <v>6509736</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123238989</v>
+        <v>123238979</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>79387</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,35 +1011,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567255</v>
+        <v>567291</v>
       </c>
       <c r="R5" t="n">
-        <v>6509736</v>
+        <v>6509745</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123238954</v>
+        <v>123220975</v>
       </c>
       <c r="B6" t="n">
-        <v>79384</v>
+        <v>83368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,44 +1117,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>1444</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567475</v>
+        <v>567466</v>
       </c>
       <c r="R6" t="n">
-        <v>6509855</v>
+        <v>6510055</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,29 +1189,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123229402</v>
+        <v>123238970</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,27 +1242,26 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567250</v>
+        <v>567256</v>
       </c>
       <c r="R7" t="n">
-        <v>6509796</v>
+        <v>6509747</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1304,28 +1299,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123218761</v>
+        <v>123229402</v>
       </c>
       <c r="B8" t="n">
-        <v>91507</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1334,41 +1330,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3884</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sjöberga, Sjöberga, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567239</v>
+        <v>567250</v>
       </c>
       <c r="R8" t="n">
-        <v>6509717</v>
+        <v>6509796</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123238970</v>
+        <v>123238960</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>79387</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,35 +1441,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567256</v>
+        <v>567474</v>
       </c>
       <c r="R9" t="n">
-        <v>6509747</v>
+        <v>6509777</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1535,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123220975</v>
+        <v>123218761</v>
       </c>
       <c r="B10" t="n">
-        <v>83365</v>
+        <v>91510</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,37 +1551,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1444</v>
+        <v>3884</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Sjöberga, Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567466</v>
+        <v>567239</v>
       </c>
       <c r="R10" t="n">
-        <v>6510055</v>
+        <v>6509717</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1637,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123238960</v>
+        <v>123238954</v>
       </c>
       <c r="B11" t="n">
-        <v>79384</v>
+        <v>79387</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567474</v>
+        <v>567475</v>
       </c>
       <c r="R11" t="n">
-        <v>6509777</v>
+        <v>6509855</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123238999</v>
+        <v>123229402</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,26 +710,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567283</v>
+        <v>567250</v>
       </c>
       <c r="R2" t="n">
-        <v>6509723</v>
+        <v>6509796</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,29 +768,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123229249</v>
+        <v>123238989</v>
       </c>
       <c r="B3" t="n">
-        <v>95139</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,41 +798,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sjöberga, Sjöberga, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567211</v>
+        <v>567255</v>
       </c>
       <c r="R3" t="n">
-        <v>6509720</v>
+        <v>6509736</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,28 +878,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123238989</v>
+        <v>123218761</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>91512</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,49 +909,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>3884</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Sjöberga, Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567255</v>
+        <v>567239</v>
       </c>
       <c r="R4" t="n">
-        <v>6509736</v>
+        <v>6509717</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,29 +981,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123238979</v>
+        <v>123238960</v>
       </c>
       <c r="B5" t="n">
-        <v>79387</v>
+        <v>79389</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567291</v>
+        <v>567474</v>
       </c>
       <c r="R5" t="n">
-        <v>6509745</v>
+        <v>6509777</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123220975</v>
+        <v>123229249</v>
       </c>
       <c r="B6" t="n">
-        <v>83368</v>
+        <v>95141</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,37 +1121,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1444</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Sjöberga, Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567466</v>
+        <v>567211</v>
       </c>
       <c r="R6" t="n">
-        <v>6510055</v>
+        <v>6509720</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123238970</v>
+        <v>123238954</v>
       </c>
       <c r="B7" t="n">
-        <v>98368</v>
+        <v>79389</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,35 +1219,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567256</v>
+        <v>567475</v>
       </c>
       <c r="R7" t="n">
-        <v>6509747</v>
+        <v>6509855</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1318,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123229402</v>
+        <v>123220975</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>83370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1330,50 +1325,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1444</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Jacq.:Fr.) Lambotte</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567250</v>
+        <v>567466</v>
       </c>
       <c r="R8" t="n">
-        <v>6509796</v>
+        <v>6510055</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123238960</v>
+        <v>123238979</v>
       </c>
       <c r="B9" t="n">
-        <v>79387</v>
+        <v>79389</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567474</v>
+        <v>567291</v>
       </c>
       <c r="R9" t="n">
-        <v>6509777</v>
+        <v>6509745</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1535,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123218761</v>
+        <v>123238999</v>
       </c>
       <c r="B10" t="n">
-        <v>91510</v>
+        <v>98370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,41 +1533,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3884</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sjöberga, Sjöberga, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567239</v>
+        <v>567283</v>
       </c>
       <c r="R10" t="n">
-        <v>6509717</v>
+        <v>6509723</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1619,28 +1613,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123238954</v>
+        <v>123238970</v>
       </c>
       <c r="B11" t="n">
-        <v>79387</v>
+        <v>98370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,30 +1644,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567475</v>
+        <v>567256</v>
       </c>
       <c r="R11" t="n">
-        <v>6509855</v>
+        <v>6509747</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123229402</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>123238989</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123218761</v>
+        <v>123220975</v>
       </c>
       <c r="B4" t="n">
-        <v>91512</v>
+        <v>83372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,37 +913,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3884</v>
+        <v>1444</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sjöberga, Sjöberga, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567239</v>
+        <v>567466</v>
       </c>
       <c r="R4" t="n">
-        <v>6509717</v>
+        <v>6510055</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123238960</v>
+        <v>123238970</v>
       </c>
       <c r="B5" t="n">
-        <v>79389</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,30 +1011,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1042,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567474</v>
+        <v>567256</v>
       </c>
       <c r="R5" t="n">
-        <v>6509777</v>
+        <v>6509747</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1105,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123229249</v>
+        <v>123238999</v>
       </c>
       <c r="B6" t="n">
-        <v>95141</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,41 +1122,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sjöberga, Sjöberga, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567211</v>
+        <v>567283</v>
       </c>
       <c r="R6" t="n">
-        <v>6509720</v>
+        <v>6509723</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,18 +1202,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1210,7 +1224,7 @@
         <v>123238954</v>
       </c>
       <c r="B7" t="n">
-        <v>79389</v>
+        <v>79390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1313,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123220975</v>
+        <v>123238960</v>
       </c>
       <c r="B8" t="n">
-        <v>83370</v>
+        <v>79390</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,41 +1339,44 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1444</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567466</v>
+        <v>567474</v>
       </c>
       <c r="R8" t="n">
-        <v>6510055</v>
+        <v>6509777</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,18 +1414,19 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1418,7 +1436,7 @@
         <v>123238979</v>
       </c>
       <c r="B9" t="n">
-        <v>79389</v>
+        <v>79390</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123238999</v>
+        <v>123229249</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>95147</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1533,49 +1551,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Sjöberga, Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567283</v>
+        <v>567211</v>
       </c>
       <c r="R10" t="n">
-        <v>6509723</v>
+        <v>6509720</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1613,29 +1623,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123238970</v>
+        <v>123218761</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>91518</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,49 +1653,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>3884</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Sjöberga, Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567256</v>
+        <v>567239</v>
       </c>
       <c r="R11" t="n">
-        <v>6509747</v>
+        <v>6509717</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1724,19 +1725,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123229402</v>
+        <v>123229249</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>95167</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Sjöberga, Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567250</v>
+        <v>567211</v>
       </c>
       <c r="R2" t="n">
-        <v>6509796</v>
+        <v>6509720</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123238979</v>
+        <v>123218761</v>
       </c>
       <c r="B3" t="n">
-        <v>79393</v>
+        <v>91538</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,44 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>3884</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Sjöberga, Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567291</v>
+        <v>567239</v>
       </c>
       <c r="R3" t="n">
-        <v>6509745</v>
+        <v>6509717</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,19 +861,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -895,7 +882,7 @@
         <v>123238960</v>
       </c>
       <c r="B4" t="n">
-        <v>79393</v>
+        <v>79399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -998,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123238954</v>
+        <v>123229402</v>
       </c>
       <c r="B5" t="n">
-        <v>79393</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,44 +997,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567475</v>
+        <v>567250</v>
       </c>
       <c r="R5" t="n">
-        <v>6509855</v>
+        <v>6509796</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,29 +1078,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123238970</v>
+        <v>123238989</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,7 +1131,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1152,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567256</v>
+        <v>567255</v>
       </c>
       <c r="R6" t="n">
-        <v>6509747</v>
+        <v>6509736</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123238989</v>
+        <v>123238999</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,7 +1242,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1263,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567255</v>
+        <v>567283</v>
       </c>
       <c r="R7" t="n">
-        <v>6509736</v>
+        <v>6509723</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123218761</v>
+        <v>123220975</v>
       </c>
       <c r="B8" t="n">
-        <v>91521</v>
+        <v>83384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,37 +1334,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3884</v>
+        <v>1444</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sjöberga, Sjöberga, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567239</v>
+        <v>567466</v>
       </c>
       <c r="R8" t="n">
-        <v>6509717</v>
+        <v>6510055</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123229249</v>
+        <v>123238970</v>
       </c>
       <c r="B9" t="n">
-        <v>95150</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,41 +1432,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sjöberga, Sjöberga, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567211</v>
+        <v>567256</v>
       </c>
       <c r="R9" t="n">
-        <v>6509720</v>
+        <v>6509747</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,28 +1512,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123238999</v>
+        <v>123238979</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>79399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,35 +1543,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1578,13 +1574,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567283</v>
+        <v>567291</v>
       </c>
       <c r="R10" t="n">
-        <v>6509723</v>
+        <v>6509745</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123220975</v>
+        <v>123238954</v>
       </c>
       <c r="B11" t="n">
-        <v>83375</v>
+        <v>79399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,41 +1649,44 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1444</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567466</v>
+        <v>567475</v>
       </c>
       <c r="R11" t="n">
-        <v>6510055</v>
+        <v>6509855</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1725,18 +1724,19 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123229249</v>
+        <v>123238954</v>
       </c>
       <c r="B2" t="n">
-        <v>95167</v>
+        <v>79404</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sjöberga, Sjöberga, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567211</v>
+        <v>567475</v>
       </c>
       <c r="R2" t="n">
-        <v>6509720</v>
+        <v>6509855</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,28 +762,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123218761</v>
+        <v>123229249</v>
       </c>
       <c r="B3" t="n">
-        <v>91538</v>
+        <v>95173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3884</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567239</v>
+        <v>567211</v>
       </c>
       <c r="R3" t="n">
-        <v>6509717</v>
+        <v>6509720</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123238960</v>
+        <v>123218761</v>
       </c>
       <c r="B4" t="n">
-        <v>79399</v>
+        <v>91543</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,44 +895,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>3884</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Sjöberga, Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567474</v>
+        <v>567239</v>
       </c>
       <c r="R4" t="n">
-        <v>6509777</v>
+        <v>6509717</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,29 +967,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123229402</v>
+        <v>123238970</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,27 +1020,26 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567250</v>
+        <v>567256</v>
       </c>
       <c r="R5" t="n">
-        <v>6509796</v>
+        <v>6509747</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,28 +1077,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123238989</v>
+        <v>123238979</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>79404</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,35 +1108,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567255</v>
+        <v>567291</v>
       </c>
       <c r="R6" t="n">
-        <v>6509736</v>
+        <v>6509745</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1207,10 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123238999</v>
+        <v>123220975</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>83389</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,46 +1214,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1444</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Jacq.:Fr.) Lambotte</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567283</v>
+        <v>567466</v>
       </c>
       <c r="R7" t="n">
-        <v>6509723</v>
+        <v>6510055</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,29 +1286,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123220975</v>
+        <v>123229402</v>
       </c>
       <c r="B8" t="n">
-        <v>83384</v>
+        <v>98502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1330,41 +1316,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1444</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567466</v>
+        <v>567250</v>
       </c>
       <c r="R8" t="n">
-        <v>6510055</v>
+        <v>6509796</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123238970</v>
+        <v>123238999</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1455,7 +1450,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1468,13 +1463,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567256</v>
+        <v>567283</v>
       </c>
       <c r="R9" t="n">
-        <v>6509747</v>
+        <v>6509723</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1531,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123238979</v>
+        <v>123238960</v>
       </c>
       <c r="B10" t="n">
-        <v>79399</v>
+        <v>79404</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1574,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567291</v>
+        <v>567474</v>
       </c>
       <c r="R10" t="n">
-        <v>6509745</v>
+        <v>6509777</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123238954</v>
+        <v>123238989</v>
       </c>
       <c r="B11" t="n">
-        <v>79399</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,30 +1644,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567475</v>
+        <v>567255</v>
       </c>
       <c r="R11" t="n">
-        <v>6509855</v>
+        <v>6509736</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123238954</v>
+        <v>123238970</v>
       </c>
       <c r="B2" t="n">
-        <v>79404</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567475</v>
+        <v>567256</v>
       </c>
       <c r="R2" t="n">
-        <v>6509855</v>
+        <v>6509747</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123229249</v>
+        <v>123238954</v>
       </c>
       <c r="B3" t="n">
-        <v>95173</v>
+        <v>79406</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,41 +798,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sjöberga, Sjöberga, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567211</v>
+        <v>567475</v>
       </c>
       <c r="R3" t="n">
-        <v>6509720</v>
+        <v>6509855</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,28 +873,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123218761</v>
+        <v>123238989</v>
       </c>
       <c r="B4" t="n">
-        <v>91543</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,41 +904,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3884</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sjöberga, Sjöberga, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567239</v>
+        <v>567255</v>
       </c>
       <c r="R4" t="n">
-        <v>6509717</v>
+        <v>6509736</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,28 +984,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123238970</v>
+        <v>123238979</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>79406</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,35 +1015,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1033,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567256</v>
+        <v>567291</v>
       </c>
       <c r="R5" t="n">
-        <v>6509747</v>
+        <v>6509745</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123238979</v>
+        <v>123229402</v>
       </c>
       <c r="B6" t="n">
-        <v>79404</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,44 +1121,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567291</v>
+        <v>567250</v>
       </c>
       <c r="R6" t="n">
-        <v>6509745</v>
+        <v>6509796</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,19 +1202,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1205,7 +1223,7 @@
         <v>123220975</v>
       </c>
       <c r="B7" t="n">
-        <v>83389</v>
+        <v>83391</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123229402</v>
+        <v>123238999</v>
       </c>
       <c r="B8" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,27 +1357,26 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567250</v>
+        <v>567283</v>
       </c>
       <c r="R8" t="n">
-        <v>6509796</v>
+        <v>6509723</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,28 +1414,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123238999</v>
+        <v>123218761</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>91545</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1427,49 +1445,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>3884</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Sjöberga, Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567283</v>
+        <v>567239</v>
       </c>
       <c r="R9" t="n">
-        <v>6509723</v>
+        <v>6509717</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,19 +1517,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1529,7 +1538,7 @@
         <v>123238960</v>
       </c>
       <c r="B10" t="n">
-        <v>79404</v>
+        <v>79406</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123238989</v>
+        <v>123229249</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>95175</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,49 +1653,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Sjöberga, Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567255</v>
+        <v>567211</v>
       </c>
       <c r="R11" t="n">
-        <v>6509736</v>
+        <v>6509720</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1724,19 +1725,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123238989</v>
+        <v>123238979</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>79406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,35 +904,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -940,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567255</v>
+        <v>567291</v>
       </c>
       <c r="R4" t="n">
-        <v>6509736</v>
+        <v>6509745</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1003,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123238979</v>
+        <v>123238989</v>
       </c>
       <c r="B5" t="n">
-        <v>79406</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,30 +1010,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567291</v>
+        <v>567255</v>
       </c>
       <c r="R5" t="n">
-        <v>6509745</v>
+        <v>6509736</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123238979</v>
+        <v>123238989</v>
       </c>
       <c r="B4" t="n">
-        <v>79406</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,30 +904,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567291</v>
+        <v>567255</v>
       </c>
       <c r="R4" t="n">
-        <v>6509745</v>
+        <v>6509736</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123238989</v>
+        <v>123238979</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>79406</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,35 +1015,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567255</v>
+        <v>567291</v>
       </c>
       <c r="R5" t="n">
-        <v>6509736</v>
+        <v>6509745</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123238970</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123238954</v>
+        <v>123238979</v>
       </c>
       <c r="B3" t="n">
         <v>79406</v>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567475</v>
+        <v>567291</v>
       </c>
       <c r="R3" t="n">
-        <v>6509855</v>
+        <v>6509745</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123238989</v>
+        <v>123229402</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,26 +927,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567255</v>
+        <v>567250</v>
       </c>
       <c r="R4" t="n">
-        <v>6509736</v>
+        <v>6509796</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,29 +985,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123238979</v>
+        <v>123238989</v>
       </c>
       <c r="B5" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,30 +1015,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1046,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567291</v>
+        <v>567255</v>
       </c>
       <c r="R5" t="n">
-        <v>6509745</v>
+        <v>6509736</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123229402</v>
+        <v>123229249</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>95683</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,47 +1126,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Sjöberga, Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567250</v>
+        <v>567211</v>
       </c>
       <c r="R6" t="n">
-        <v>6509796</v>
+        <v>6509720</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1220,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123220975</v>
+        <v>123218761</v>
       </c>
       <c r="B7" t="n">
-        <v>83391</v>
+        <v>91545</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,37 +1232,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1444</v>
+        <v>3884</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Sjöberga, Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567466</v>
+        <v>567239</v>
       </c>
       <c r="R7" t="n">
-        <v>6510055</v>
+        <v>6509717</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,7 +1321,7 @@
         <v>123238999</v>
       </c>
       <c r="B8" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123218761</v>
+        <v>123238960</v>
       </c>
       <c r="B9" t="n">
-        <v>91545</v>
+        <v>79406</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,41 +1441,44 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3884</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sjöberga, Sjöberga, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567239</v>
+        <v>567474</v>
       </c>
       <c r="R9" t="n">
-        <v>6509717</v>
+        <v>6509777</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1517,28 +1516,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123238960</v>
+        <v>123220975</v>
       </c>
       <c r="B10" t="n">
-        <v>79406</v>
+        <v>83391</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,44 +1547,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1444</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567474</v>
+        <v>567466</v>
       </c>
       <c r="R10" t="n">
-        <v>6509777</v>
+        <v>6510055</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1622,29 +1619,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123229249</v>
+        <v>123238954</v>
       </c>
       <c r="B11" t="n">
-        <v>95175</v>
+        <v>79406</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,41 +1649,44 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sjöberga, Sjöberga, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567211</v>
+        <v>567475</v>
       </c>
       <c r="R11" t="n">
-        <v>6509720</v>
+        <v>6509855</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1725,18 +1724,19 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1741,6 +1741,131 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124817784</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skogen norr om Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>567372</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6509914</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -1746,7 +1746,7 @@
         <v>124817784</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1866,6 +1866,321 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129273439</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92864</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skogen norr om Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>567418</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6509855</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129273612</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92864</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skogen norr om Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>567461</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6509803</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129273307</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92864</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skogen norr om Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>567501</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6509743</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -1871,7 +1871,7 @@
         <v>129273439</v>
       </c>
       <c r="B13" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129273612</v>
       </c>
       <c r="B14" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129273307</v>
       </c>
       <c r="B15" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -1871,7 +1871,7 @@
         <v>129273439</v>
       </c>
       <c r="B13" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129273612</v>
       </c>
       <c r="B14" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129273307</v>
       </c>
       <c r="B15" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -1871,7 +1871,7 @@
         <v>129273439</v>
       </c>
       <c r="B13" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129273612</v>
       </c>
       <c r="B14" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129273307</v>
       </c>
       <c r="B15" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -1871,7 +1871,7 @@
         <v>129273439</v>
       </c>
       <c r="B13" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129273612</v>
       </c>
       <c r="B14" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129273307</v>
       </c>
       <c r="B15" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -1871,7 +1871,7 @@
         <v>129273439</v>
       </c>
       <c r="B13" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129273612</v>
       </c>
       <c r="B14" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129273307</v>
       </c>
       <c r="B15" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -1871,7 +1871,7 @@
         <v>129273439</v>
       </c>
       <c r="B13" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129273612</v>
       </c>
       <c r="B14" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129273307</v>
       </c>
       <c r="B15" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -1871,7 +1871,7 @@
         <v>129273439</v>
       </c>
       <c r="B13" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129273612</v>
       </c>
       <c r="B14" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129273307</v>
       </c>
       <c r="B15" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -1871,7 +1871,7 @@
         <v>129273439</v>
       </c>
       <c r="B13" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129273612</v>
       </c>
       <c r="B14" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129273307</v>
       </c>
       <c r="B15" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -1871,7 +1871,7 @@
         <v>129273439</v>
       </c>
       <c r="B13" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129273612</v>
       </c>
       <c r="B14" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129273307</v>
       </c>
       <c r="B15" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -1871,7 +1871,7 @@
         <v>129273439</v>
       </c>
       <c r="B13" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129273612</v>
       </c>
       <c r="B14" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129273307</v>
       </c>
       <c r="B15" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -1871,7 +1871,7 @@
         <v>129273439</v>
       </c>
       <c r="B13" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129273612</v>
       </c>
       <c r="B14" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129273307</v>
       </c>
       <c r="B15" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -1871,7 +1871,7 @@
         <v>129273439</v>
       </c>
       <c r="B13" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129273612</v>
       </c>
       <c r="B14" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129273307</v>
       </c>
       <c r="B15" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2181,6 +2181,226 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129962159</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>567259</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6509842</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129962211</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>567241</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6509839</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2186,7 +2186,7 @@
         <v>129962159</v>
       </c>
       <c r="B16" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>129962211</v>
       </c>
       <c r="B17" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2400,6 +2400,116 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130011625</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98797</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>567222</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6509744</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -2186,7 +2186,7 @@
         <v>129962159</v>
       </c>
       <c r="B16" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>129962211</v>
       </c>
       <c r="B17" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>130011625</v>
       </c>
       <c r="B18" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2511,6 +2511,226 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130077789</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98802</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Strax öster om nedre Vekmangeln, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>567243</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6509782</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130077782</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98802</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Strax öster om nedre Vekmangeln, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>567286</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6509786</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -2186,7 +2186,7 @@
         <v>129962159</v>
       </c>
       <c r="B16" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>129962211</v>
       </c>
       <c r="B17" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>130011625</v>
       </c>
       <c r="B18" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>130077789</v>
       </c>
       <c r="B19" t="n">
-        <v>98802</v>
+        <v>98815</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>130077782</v>
       </c>
       <c r="B20" t="n">
-        <v>98802</v>
+        <v>98815</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -2186,7 +2186,7 @@
         <v>129962159</v>
       </c>
       <c r="B16" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>129962211</v>
       </c>
       <c r="B17" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>130011625</v>
       </c>
       <c r="B18" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>130077789</v>
       </c>
       <c r="B19" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>130077782</v>
       </c>
       <c r="B20" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -2186,7 +2186,7 @@
         <v>129962159</v>
       </c>
       <c r="B16" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>129962211</v>
       </c>
       <c r="B17" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>130011625</v>
       </c>
       <c r="B18" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>130077789</v>
       </c>
       <c r="B19" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>130077782</v>
       </c>
       <c r="B20" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3310,6 +3310,226 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131376348</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99019</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>567268</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6509739</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131375981</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99019</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>567307</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6509703</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -2736,7 +2736,7 @@
         <v>131191199</v>
       </c>
       <c r="B21" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>131271025</v>
       </c>
       <c r="B22" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>131289488</v>
       </c>
       <c r="B23" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>131305445</v>
       </c>
       <c r="B24" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>131305275</v>
       </c>
       <c r="B25" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>131376348</v>
       </c>
       <c r="B26" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>131375981</v>
       </c>
       <c r="B27" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -2736,7 +2736,7 @@
         <v>131191199</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>131271025</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>131289488</v>
       </c>
       <c r="B23" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>131305445</v>
       </c>
       <c r="B24" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>131305275</v>
       </c>
       <c r="B25" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>131376348</v>
       </c>
       <c r="B26" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>131375981</v>
       </c>
       <c r="B27" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -2736,7 +2736,7 @@
         <v>131191199</v>
       </c>
       <c r="B21" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>131271025</v>
       </c>
       <c r="B22" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>131289488</v>
       </c>
       <c r="B23" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>131305445</v>
       </c>
       <c r="B24" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>131305275</v>
       </c>
       <c r="B25" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>131376348</v>
       </c>
       <c r="B26" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>131375981</v>
       </c>
       <c r="B27" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>131528133</v>
       </c>
       <c r="B28" t="n">
-        <v>101231</v>
+        <v>101237</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>131528172</v>
       </c>
       <c r="B29" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>131528130</v>
       </c>
       <c r="B30" t="n">
-        <v>101231</v>
+        <v>101237</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3847,6 +3847,116 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131698144</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99033</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>567259</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6509719</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -3315,7 +3315,7 @@
         <v>131376348</v>
       </c>
       <c r="B26" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>131375981</v>
       </c>
       <c r="B27" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>131528133</v>
       </c>
       <c r="B28" t="n">
-        <v>101237</v>
+        <v>101238</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>131528130</v>
       </c>
       <c r="B30" t="n">
-        <v>101237</v>
+        <v>101238</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>131698144</v>
       </c>
       <c r="B31" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -2845,7 +2845,7 @@
         <v>131271025</v>
       </c>
       <c r="B22" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>131289488</v>
       </c>
       <c r="B23" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>131305445</v>
       </c>
       <c r="B24" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>131305275</v>
       </c>
       <c r="B25" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>131376348</v>
       </c>
       <c r="B26" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>131375981</v>
       </c>
       <c r="B27" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>131528133</v>
       </c>
       <c r="B28" t="n">
-        <v>101238</v>
+        <v>101239</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>131528172</v>
       </c>
       <c r="B29" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>131528130</v>
       </c>
       <c r="B30" t="n">
-        <v>101238</v>
+        <v>101239</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>131698144</v>
       </c>
       <c r="B31" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -2845,7 +2845,7 @@
         <v>131271025</v>
       </c>
       <c r="B22" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>131289488</v>
       </c>
       <c r="B23" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>131305445</v>
       </c>
       <c r="B24" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>131305275</v>
       </c>
       <c r="B25" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>131376348</v>
       </c>
       <c r="B26" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>131375981</v>
       </c>
       <c r="B27" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>131528133</v>
       </c>
       <c r="B28" t="n">
-        <v>101239</v>
+        <v>101242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>131528172</v>
       </c>
       <c r="B29" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>131528130</v>
       </c>
       <c r="B30" t="n">
-        <v>101239</v>
+        <v>101242</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>131698144</v>
       </c>
       <c r="B31" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -3535,7 +3535,7 @@
         <v>131528133</v>
       </c>
       <c r="B28" t="n">
-        <v>101242</v>
+        <v>101243</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>131528130</v>
       </c>
       <c r="B30" t="n">
-        <v>101242</v>
+        <v>101243</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3957,6 +3957,226 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131906000</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57900</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skogen norr om Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>567385</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6509905</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska spår i basen på tre döda granar</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131905519</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57900</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skogen norr om Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>567371</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6509850</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska spår i basen på fem döda granar</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -2954,7 +2954,7 @@
         <v>131289488</v>
       </c>
       <c r="B23" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>131305445</v>
       </c>
       <c r="B24" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>131305275</v>
       </c>
       <c r="B25" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>131376348</v>
       </c>
       <c r="B26" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>131375981</v>
       </c>
       <c r="B27" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>131528133</v>
       </c>
       <c r="B28" t="n">
-        <v>101243</v>
+        <v>101249</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>131528172</v>
       </c>
       <c r="B29" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>131528130</v>
       </c>
       <c r="B30" t="n">
-        <v>101243</v>
+        <v>101249</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>131698144</v>
       </c>
       <c r="B31" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>131906000</v>
       </c>
       <c r="B32" t="n">
-        <v>57900</v>
+        <v>57901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>131905519</v>
       </c>
       <c r="B33" t="n">
-        <v>57900</v>
+        <v>57901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4177,6 +4177,111 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131992900</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58065</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Söder om Björkliden, Ög</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>567441</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6509983</v>
+      </c>
+      <c r="S34" t="n">
+        <v>50</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4282,6 +4282,112 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132024477</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99046</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Söder om Björkliden, Ög</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>567445</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6509930</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3535,7 +3535,7 @@
         <v>131528133</v>
       </c>
       <c r="B28" t="n">
-        <v>101249</v>
+        <v>101252</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>131528172</v>
       </c>
       <c r="B29" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>131528130</v>
       </c>
       <c r="B30" t="n">
-        <v>101249</v>
+        <v>101252</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>131698144</v>
       </c>
       <c r="B31" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>131906000</v>
       </c>
       <c r="B32" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>131905519</v>
       </c>
       <c r="B33" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>131992900</v>
       </c>
       <c r="B34" t="n">
-        <v>58065</v>
+        <v>58066</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>132024477</v>
       </c>
       <c r="B35" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4388,6 +4388,111 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132110114</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57904</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skogen norr om Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>567517</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6509795</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -3535,7 +3535,7 @@
         <v>131528133</v>
       </c>
       <c r="B28" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>131528172</v>
       </c>
       <c r="B29" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>131528130</v>
       </c>
       <c r="B30" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>131698144</v>
       </c>
       <c r="B31" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>131906000</v>
       </c>
       <c r="B32" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>131905519</v>
       </c>
       <c r="B33" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>131992900</v>
       </c>
       <c r="B34" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>132024477</v>
       </c>
       <c r="B35" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>132110114</v>
       </c>
       <c r="B36" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -3852,7 +3852,7 @@
         <v>131698144</v>
       </c>
       <c r="B31" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>131992900</v>
       </c>
       <c r="B34" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>132024477</v>
       </c>
       <c r="B35" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4493,6 +4493,121 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132477944</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skogen norr om Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>567461</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6509803</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4608,6 +4608,116 @@
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132618661</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Öster om Nedre Vekmangeln, Ög</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>567299</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6509708</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -3962,7 +3962,7 @@
         <v>131906000</v>
       </c>
       <c r="B32" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>131905519</v>
       </c>
       <c r="B33" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>131992900</v>
       </c>
       <c r="B34" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>132024477</v>
       </c>
       <c r="B35" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>132110114</v>
       </c>
       <c r="B36" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>132477944</v>
       </c>
       <c r="B37" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>132618661</v>
       </c>
       <c r="B38" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -4182,7 +4182,7 @@
         <v>131992900</v>
       </c>
       <c r="B34" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>132024477</v>
       </c>
       <c r="B35" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>132110114</v>
       </c>
       <c r="B36" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>132477944</v>
       </c>
       <c r="B37" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>132618661</v>
       </c>
       <c r="B38" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -4613,7 +4613,7 @@
         <v>132618661</v>
       </c>
       <c r="B38" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -4287,7 +4287,7 @@
         <v>132024477</v>
       </c>
       <c r="B35" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>132618661</v>
       </c>
       <c r="B38" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -4393,7 +4393,7 @@
         <v>132110114</v>
       </c>
       <c r="B36" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>132477944</v>
       </c>
       <c r="B37" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>132618661</v>
       </c>
       <c r="B38" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -4613,7 +4613,7 @@
         <v>132618661</v>
       </c>
       <c r="B38" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -4613,7 +4613,7 @@
         <v>132618661</v>
       </c>
       <c r="B38" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4718,6 +4718,111 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>133035794</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58637</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Söder om Björkliden, Ög</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>567441</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6509983</v>
+      </c>
+      <c r="S39" t="n">
+        <v>50</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -4498,7 +4498,7 @@
         <v>132477944</v>
       </c>
       <c r="B37" t="n">
-        <v>57951</v>
+        <v>57954</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>132618661</v>
       </c>
       <c r="B38" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>133035794</v>
       </c>
       <c r="B39" t="n">
-        <v>58637</v>
+        <v>58640</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -4613,7 +4613,7 @@
         <v>132618661</v>
       </c>
       <c r="B38" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -4498,7 +4498,7 @@
         <v>132477944</v>
       </c>
       <c r="B37" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>132618661</v>
       </c>
       <c r="B38" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>133035794</v>
       </c>
       <c r="B39" t="n">
-        <v>58640</v>
+        <v>58641</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123238970</v>
+        <v>123220975</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1444</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Jacq.:Fr.) Lambotte</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567256</v>
+        <v>567466</v>
       </c>
       <c r="R2" t="n">
-        <v>6509747</v>
+        <v>6510055</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,75 +754,66 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123238979</v>
+        <v>123229249</v>
       </c>
       <c r="B3" t="n">
-        <v>79406</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Sjöberga, Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567291</v>
+        <v>567211</v>
       </c>
       <c r="R3" t="n">
-        <v>6509745</v>
+        <v>6509720</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,78 +851,63 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123229402</v>
+        <v>123222310</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567250</v>
+        <v>567459</v>
       </c>
       <c r="R4" t="n">
-        <v>6509796</v>
+        <v>6510087</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1003,61 +966,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123238989</v>
+        <v>123222346</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2668</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567255</v>
+        <v>567459</v>
       </c>
       <c r="R5" t="n">
-        <v>6509736</v>
+        <v>6510087</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,34 +1045,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123229249</v>
+        <v>123238588</v>
       </c>
       <c r="B6" t="n">
-        <v>95683</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,37 +1074,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>2668</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sjöberga, Sjöberga, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567211</v>
+        <v>567456</v>
       </c>
       <c r="R6" t="n">
-        <v>6509720</v>
+        <v>6510083</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,33 +1146,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123218761</v>
+        <v>123221824</v>
       </c>
       <c r="B7" t="n">
-        <v>91545</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1232,37 +1176,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3884</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sjöberga, Sjöberga, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567239</v>
+        <v>567459</v>
       </c>
       <c r="R7" t="n">
-        <v>6509717</v>
+        <v>6510087</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,61 +1262,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123238999</v>
+        <v>123218761</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>3884</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Sjöberga, Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567283</v>
+        <v>567239</v>
       </c>
       <c r="R8" t="n">
-        <v>6509723</v>
+        <v>6509717</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1410,34 +1341,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123238960</v>
+        <v>129273307</v>
       </c>
       <c r="B9" t="n">
-        <v>79406</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,40 +1370,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Skogen norr om Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567474</v>
+        <v>567501</v>
       </c>
       <c r="R9" t="n">
-        <v>6509777</v>
+        <v>6509743</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1502,12 +1431,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,62 +1452,64 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123220975</v>
+        <v>129273439</v>
       </c>
       <c r="B10" t="n">
-        <v>83391</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1444</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hultagölen, Hultagölen, Ög</t>
+          <t>Skogen norr om Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567466</v>
+        <v>567418</v>
       </c>
       <c r="R10" t="n">
-        <v>6510055</v>
+        <v>6509855</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1605,12 +1536,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1619,33 +1550,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123238954</v>
+        <v>129273612</v>
       </c>
       <c r="B11" t="n">
-        <v>79406</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,40 +1580,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nedre Vekmangeln, Ög</t>
+          <t>Skogen norr om Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567475</v>
+        <v>567461</v>
       </c>
       <c r="R11" t="n">
-        <v>6509855</v>
+        <v>6509803</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1710,12 +1641,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1731,77 +1662,63 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124817784</v>
+        <v>123238954</v>
       </c>
       <c r="B12" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skogen norr om Sjöberga, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567372</v>
+        <v>567475</v>
       </c>
       <c r="R12" t="n">
-        <v>6509914</v>
+        <v>6509855</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1825,22 +1742,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,22 +1763,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129273439</v>
+        <v>123238960</v>
       </c>
       <c r="B13" t="n">
-        <v>92908</v>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1879,44 +1786,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skogen norr om Sjöberga, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567418</v>
+        <v>567474</v>
       </c>
       <c r="R13" t="n">
-        <v>6509855</v>
+        <v>6509777</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1940,12 +1843,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1961,22 +1864,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129273612</v>
+        <v>123238979</v>
       </c>
       <c r="B14" t="n">
-        <v>92908</v>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,44 +1887,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skogen norr om Sjöberga, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567461</v>
+        <v>567291</v>
       </c>
       <c r="R14" t="n">
-        <v>6509803</v>
+        <v>6509745</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2045,12 +1944,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,53 +1965,58 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129273307</v>
+        <v>131191199</v>
       </c>
       <c r="B15" t="n">
-        <v>92908</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2120,10 +2024,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567501</v>
+        <v>567418</v>
       </c>
       <c r="R15" t="n">
-        <v>6509743</v>
+        <v>6509855</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,12 +2054,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2164,7 +2068,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2183,57 +2086,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129962159</v>
+        <v>131236926</v>
       </c>
       <c r="B16" t="n">
-        <v>98920</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+          <t>Sydost Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567259</v>
+        <v>567473</v>
       </c>
       <c r="R16" t="n">
-        <v>6509842</v>
+        <v>6510086</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,12 +2159,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Flera grova aspar lämpliga för bobygge i anslutning. Varav åtminstone två med äldre bohål.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2274,7 +2178,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2293,60 +2196,60 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129962211</v>
+        <v>131271025</v>
       </c>
       <c r="B17" t="n">
-        <v>98920</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+          <t>Vid Lillebo, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567241</v>
+        <v>567427</v>
       </c>
       <c r="R17" t="n">
-        <v>6509839</v>
+        <v>6510021</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2370,12 +2273,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2384,7 +2287,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2403,57 +2305,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130011625</v>
+        <v>131289488</v>
       </c>
       <c r="B18" t="n">
-        <v>98920</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+          <t>Skogen norr om Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567222</v>
+        <v>567462</v>
       </c>
       <c r="R18" t="n">
-        <v>6509744</v>
+        <v>6509761</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,12 +2378,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,7 +2392,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2513,57 +2410,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130077789</v>
+        <v>131305275</v>
       </c>
       <c r="B19" t="n">
-        <v>98920</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Strax öster om nedre Vekmangeln, Ög</t>
+          <t>Strax öster om Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567243</v>
+        <v>567295</v>
       </c>
       <c r="R19" t="n">
-        <v>6509782</v>
+        <v>6509935</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2590,12 +2487,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Flög upp när vi passerade på stigen.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,7 +2516,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2623,57 +2534,65 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130077782</v>
+        <v>131305445</v>
       </c>
       <c r="B20" t="n">
-        <v>98920</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Strax öster om nedre Vekmangeln, Ög</t>
+          <t>Strax öster om Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567286</v>
+        <v>567240</v>
       </c>
       <c r="R20" t="n">
-        <v>6509786</v>
+        <v>6509739</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2700,12 +2619,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2714,7 +2648,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2733,14 +2666,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131191199</v>
+        <v>131528169</v>
       </c>
       <c r="B21" t="n">
-        <v>57895</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2761,29 +2694,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skogen norr om Sjöberga, Ög</t>
+          <t>Strax öster om Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>567418</v>
+        <v>567281</v>
       </c>
       <c r="R21" t="n">
-        <v>6509855</v>
+        <v>6509958</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2810,12 +2739,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2842,14 +2771,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131271025</v>
+        <v>131528172</v>
       </c>
       <c r="B22" t="n">
-        <v>57899</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2875,24 +2804,20 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vid Lillebo, Ög</t>
+          <t>Strax öster om Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>567427</v>
+        <v>567262</v>
       </c>
       <c r="R22" t="n">
-        <v>6510021</v>
+        <v>6509765</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2919,12 +2844,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2951,14 +2876,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131289488</v>
+        <v>131905519</v>
       </c>
       <c r="B23" t="n">
-        <v>57901</v>
+        <v>57972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2984,7 +2909,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2994,10 +2919,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567462</v>
+        <v>567371</v>
       </c>
       <c r="R23" t="n">
-        <v>6509761</v>
+        <v>6509850</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3024,12 +2949,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska spår i basen på fem döda granar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3056,14 +2986,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131305445</v>
+        <v>131906000</v>
       </c>
       <c r="B24" t="n">
-        <v>57901</v>
+        <v>57972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3084,37 +3014,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+          <t>Skogen norr om Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567240</v>
+        <v>567385</v>
       </c>
       <c r="R24" t="n">
-        <v>6509739</v>
+        <v>6509905</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3141,27 +3059,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Färska spår i basen på tre döda granar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,14 +3096,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131305275</v>
+        <v>132110114</v>
       </c>
       <c r="B25" t="n">
-        <v>57901</v>
+        <v>57972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3218,30 +3126,26 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+          <t>Skogen norr om Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>567295</v>
+        <v>567517</v>
       </c>
       <c r="R25" t="n">
-        <v>6509935</v>
+        <v>6509795</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3265,27 +3169,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Flög upp när vi passerade på stigen.</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3312,57 +3201,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131376348</v>
+        <v>132477944</v>
       </c>
       <c r="B26" t="n">
-        <v>99044</v>
+        <v>57972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+          <t>Skogen norr om Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567268</v>
+        <v>567461</v>
       </c>
       <c r="R26" t="n">
-        <v>6509739</v>
+        <v>6509803</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3389,12 +3274,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3403,7 +3298,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3422,60 +3316,56 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131375981</v>
+        <v>133695305</v>
       </c>
       <c r="B27" t="n">
-        <v>99044</v>
+        <v>58260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103012</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+          <t>Söder om Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567307</v>
+        <v>567489</v>
       </c>
       <c r="R27" t="n">
-        <v>6509703</v>
+        <v>6509961</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3499,12 +3389,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3513,7 +3403,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3532,56 +3421,56 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131528133</v>
+        <v>131992900</v>
       </c>
       <c r="B28" t="n">
-        <v>101260</v>
+        <v>58136</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+          <t>Söder om Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567205</v>
+        <v>567441</v>
       </c>
       <c r="R28" t="n">
-        <v>6509690</v>
+        <v>6509983</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3605,12 +3494,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3619,7 +3508,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3638,32 +3526,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131528172</v>
+        <v>133035839</v>
       </c>
       <c r="B29" t="n">
-        <v>57911</v>
+        <v>58596</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>103041</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3671,23 +3559,23 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+          <t>Söder om Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>567262</v>
+        <v>567441</v>
       </c>
       <c r="R29" t="n">
-        <v>6509765</v>
+        <v>6509983</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3711,12 +3599,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3743,10 +3631,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131528130</v>
+        <v>133035794</v>
       </c>
       <c r="B30" t="n">
-        <v>101260</v>
+        <v>58658</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3754,45 +3642,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+          <t>Söder om Björkliden, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567207</v>
+        <v>567441</v>
       </c>
       <c r="R30" t="n">
-        <v>6509710</v>
+        <v>6509983</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3816,12 +3704,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3830,7 +3718,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3849,10 +3736,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131698144</v>
+        <v>123229402</v>
       </c>
       <c r="B31" t="n">
-        <v>99098</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,7 +3766,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3887,22 +3774,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+          <t>Hultagölen, Hultagölen, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567259</v>
+        <v>567250</v>
       </c>
       <c r="R31" t="n">
-        <v>6509719</v>
+        <v>6509796</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3926,12 +3810,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3940,75 +3824,74 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131906000</v>
+        <v>123238970</v>
       </c>
       <c r="B32" t="n">
-        <v>57946</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skogen norr om Sjöberga, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567385</v>
+        <v>567256</v>
       </c>
       <c r="R32" t="n">
-        <v>6509905</v>
+        <v>6509747</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4032,17 +3915,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska spår i basen på tre döda granar</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4051,74 +3929,75 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131905519</v>
+        <v>123238989</v>
       </c>
       <c r="B33" t="n">
-        <v>57946</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skogen norr om Sjöberga, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567371</v>
+        <v>567255</v>
       </c>
       <c r="R33" t="n">
-        <v>6509850</v>
+        <v>6509736</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4142,17 +4021,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska spår i basen på fem döda granar</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4161,74 +4035,75 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131992900</v>
+        <v>123238999</v>
       </c>
       <c r="B34" t="n">
-        <v>58114</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Söder om Björkliden, Ög</t>
+          <t>Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>567441</v>
+        <v>567283</v>
       </c>
       <c r="R34" t="n">
-        <v>6509983</v>
+        <v>6509723</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4252,12 +4127,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4266,25 +4141,26 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Andreas Larsson, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132024477</v>
+        <v>124817784</v>
       </c>
       <c r="B35" t="n">
         <v>99118</v>
@@ -4314,26 +4190,30 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Söder om Björkliden, Ög</t>
+          <t>Skogen norr om Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>567445</v>
+        <v>567372</v>
       </c>
       <c r="R35" t="n">
-        <v>6509930</v>
+        <v>6509914</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4357,12 +4237,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4390,56 +4280,60 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132110114</v>
+        <v>129962159</v>
       </c>
       <c r="B36" t="n">
-        <v>57951</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skogen norr om Sjöberga, Ög</t>
+          <t>Strax öster om Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>567517</v>
+        <v>567259</v>
       </c>
       <c r="R36" t="n">
-        <v>6509795</v>
+        <v>6509842</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4463,12 +4357,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4477,6 +4371,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4495,53 +4390,57 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132477944</v>
+        <v>129962211</v>
       </c>
       <c r="B37" t="n">
-        <v>57955</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skogen norr om Sjöberga, Ög</t>
+          <t>Strax öster om Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>567461</v>
+        <v>567241</v>
       </c>
       <c r="R37" t="n">
-        <v>6509803</v>
+        <v>6509839</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4568,22 +4467,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:45</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4592,6 +4481,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4610,10 +4500,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132618661</v>
+        <v>130011625</v>
       </c>
       <c r="B38" t="n">
-        <v>99130</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4640,7 +4530,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4653,14 +4543,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Öster om Nedre Vekmangeln, Ög</t>
+          <t>Strax öster om Nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>567299</v>
+        <v>567222</v>
       </c>
       <c r="R38" t="n">
-        <v>6509708</v>
+        <v>6509744</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4687,12 +4577,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4720,56 +4610,60 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133035794</v>
+        <v>130077782</v>
       </c>
       <c r="B39" t="n">
-        <v>58641</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Söder om Björkliden, Ög</t>
+          <t>Strax öster om nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>567441</v>
+        <v>567286</v>
       </c>
       <c r="R39" t="n">
-        <v>6509983</v>
+        <v>6509786</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4793,12 +4687,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4807,6 +4701,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4825,56 +4720,60 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133695305</v>
+        <v>130077789</v>
       </c>
       <c r="B40" t="n">
-        <v>58260</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103012</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Söder om Björkliden, Ög</t>
+          <t>Strax öster om nedre Vekmangeln, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>567489</v>
+        <v>567243</v>
       </c>
       <c r="R40" t="n">
-        <v>6509961</v>
+        <v>6509782</v>
       </c>
       <c r="S40" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4898,12 +4797,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4912,6 +4811,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4927,6 +4827,870 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131375981</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>567307</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6509703</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131376348</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>567268</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6509739</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131698144</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>567259</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6509719</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132024477</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Söder om Björkliden, Ög</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>567445</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6509930</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132618661</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Öster om Nedre Vekmangeln, Ög</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>567299</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6509708</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131528130</v>
+      </c>
+      <c r="B46" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>567207</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6509710</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>131528133</v>
+      </c>
+      <c r="B47" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Strax öster om Nedre Vekmangeln, Ög</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>567205</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6509690</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>133695480</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Söder om Björkliden, Ög</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>567470</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6510067</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11109-2025 artfynd.xlsx
+++ b/artfynd/A 11109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123220975</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123229249</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123222310</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123222346</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123238588</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123221824</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123218761</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1461,6 +1501,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129273307</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1566,6 +1611,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129273439</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1671,6 +1721,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129273612</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1772,6 +1827,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123238954</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1873,6 +1933,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123238960</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1974,6 +2039,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123238979</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2083,6 +2153,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131191199</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2193,6 +2268,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131236926</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2302,6 +2382,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131271025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2407,6 +2492,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131289488</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2531,6 +2621,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131305275</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2663,6 +2758,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131305445</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2768,6 +2868,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131528169</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2873,6 +2978,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131528172</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2983,6 +3093,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131905519</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3093,6 +3208,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131906000</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3198,6 +3318,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132110114</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3313,6 +3438,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132477944</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3418,6 +3548,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133695305</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3523,6 +3658,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131992900</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3628,6 +3768,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133035839</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3733,6 +3878,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133035794</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3839,6 +3989,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123229402</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3945,6 +4100,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123238970</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4051,6 +4211,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123238989</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4157,6 +4322,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123238999</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4277,6 +4447,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124817784</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4387,6 +4562,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962159</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4497,6 +4677,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962211</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4607,6 +4792,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130011625</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4717,6 +4907,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130077782</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4827,6 +5022,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130077789</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4937,6 +5137,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131375981</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5047,6 +5252,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131376348</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5157,6 +5367,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131698144</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5263,6 +5478,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132024477</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5373,6 +5593,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132618661</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5479,6 +5704,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131528130</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5585,6 +5815,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131528133</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5691,8 +5926,62 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133695480</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>